--- a/artfynd/A 16870-2025 artfynd.xlsx
+++ b/artfynd/A 16870-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>109722310</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688578.5776470583</v>
+        <v>688579</v>
       </c>
       <c r="R2" t="n">
-        <v>6636441.823663246</v>
+        <v>6636442</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,6 +779,228 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69542792</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99532</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219879</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Getrams</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Polygonatum odoratum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Mill.) Druce</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NNV om Kalkmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>688337</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6637014</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2003-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Dikeskant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>69542777</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NNV om Kalkmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>688387</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6636967</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2003-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Skogsdike</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16870-2025 artfynd.xlsx
+++ b/artfynd/A 16870-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69542792</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69542777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>